--- a/evaluation_multimodels/runs/2026-09-21-minimal32-five-self-included/pairs/gemini_gemini-3-pro-preview-thinking_judge_medium__vs__gpt_gpt-5.6-sol_judge_medium.xlsx
+++ b/evaluation_multimodels/runs/2026-09-21-minimal32-five-self-included/pairs/gemini_gemini-3-pro-preview-thinking_judge_medium__vs__gpt_gpt-5.6-sol_judge_medium.xlsx
@@ -3064,17 +3064,17 @@
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>34395.24574996904</v>
+        <v>4300.917791028041</v>
       </c>
       <c r="M9" t="n">
-        <v>549589.4978339784</v>
+        <v>1933.808750007302</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>["RemoteDisconnected", "TimeoutError", "TimeoutError", "TimeoutError", "TimeoutError"]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -3114,12 +3114,12 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>TIMEOUT</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>ProviderCallError: gpt transport failed: TimeoutError: The read operation timed out</t>
+          <t>ProviderCallError: gpt transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
